--- a/docs/downloads/经营分_津河省区__廊坊片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__廊坊片区_2026-10-19.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -2688,20 +2688,24 @@
           <t>廊坊片区</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>廊坊市</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7205884105198667776</t>
+          <t>7148806097401301025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>锦江都城永清大兴国际机场酒店</t>
+          <t>7天酒店·固安南关夜市北京野生动物园店</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>金鑫·漫酒店</t>
+          <t>7天酒店(固安大兴国际机场新源街店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2710,14 +2714,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2727,19 +2731,19 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2779,17 +2783,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7148806097401301025</t>
+          <t>6601144502256142344</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7天酒店·固安南关夜市北京野生动物园店</t>
+          <t>锦江之星霸州高铁站益津南路酒店</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7天酒店(固安大兴国际机场新源街店)</t>
+          <t>锦江之星(霸州高铁站益津南路店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2815,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2827,7 +2831,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2867,33 +2871,33 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601144502256142344</t>
+          <t>6798708712447019012</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星霸州高铁站益津南路酒店</t>
+          <t>7天酒店(廊坊霸州胜芳店)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星(霸州高铁站益津南路店)</t>
+          <t>7天酒店(廊坊霸州胜芳店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2903,13 +2907,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -3673,13 +3677,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3704,26 +3708,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>组织门店未匹配经营分</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>7364999679521589298</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>中国区经营分文件中未找到该 POI</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>